--- a/data/Budget_Architettura.xlsx
+++ b/data/Budget_Architettura.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30002"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F378F6BF-3224-45C8-B2B8-53F5E29598FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Utility\Macchine Virtuali\cartellaCondivisa\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86090DD-8631-481C-B83C-E2A5D7714AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1830" yWindow="3480" windowWidth="25425" windowHeight="13455" xr2:uid="{DAE9AE39-AD6B-3749-86A8-21CD970B6B04}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,44 +36,60 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>supporto contratti</t>
-  </si>
-  <si>
-    <t>supporto studenti</t>
-  </si>
-  <si>
-    <t>conferenze</t>
-  </si>
-  <si>
-    <t>tutorato studenti</t>
-  </si>
-  <si>
-    <t>tutorato dottorandi</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>Nome</t>
+  </si>
+  <si>
+    <t>Supporto contratti</t>
+  </si>
+  <si>
+    <t>Costo €/h</t>
+  </si>
+  <si>
+    <t>Supporto studenti</t>
+  </si>
+  <si>
+    <t>Conferenze</t>
+  </si>
+  <si>
+    <t>Tutorato studenti</t>
+  </si>
+  <si>
+    <t>Tutorato dottorandi</t>
+  </si>
+  <si>
+    <t>Con Spesa</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$€-410]_-;\-* #,##0.00\ [$€-410]_-;_-* &quot;-&quot;??\ [$€-410]_-;_-@_-"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="14"/>
       <color theme="1"/>
-      <name val="Avenir Next LT Pro"/>
+      <name val="Aptos Narrow (Corpo)"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -91,17 +112,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -113,8 +150,25 @@
 </styleSheet>
 </file>
 
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -124,39 +178,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -208,7 +262,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -319,13 +373,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -334,6 +381,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -398,63 +452,114 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C88EBB4-D3B1-5A40-8426-3D3641BA2EA1}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" customWidth="1"/>
+    <col min="1" max="1" width="20.625" customWidth="1"/>
+    <col min="2" max="2" width="16.625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" ht="12.75">
+    <row r="1" spans="1:3" s="3" customFormat="1" ht="18.75">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="B2" s="4">
+        <v>31.71</v>
+      </c>
+      <c r="C2" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="B3" s="5">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
+      <c r="B4" s="4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" s="3" customFormat="1">
-      <c r="A2" s="1">
-        <v>32</v>
-      </c>
-      <c r="B2" s="1">
-        <v>7</v>
-      </c>
-      <c r="C2" s="1">
-        <v>0</v>
-      </c>
-      <c r="D2" s="1">
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="4">
         <v>20</v>
       </c>
-      <c r="E2" s="1">
+      <c r="C5" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="4">
         <v>15</v>
+      </c>
+      <c r="C6" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>